--- a/important_mails_2026-05-23.xlsx
+++ b/important_mails_2026-05-23.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2202,7 +2202,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2217,70 +2217,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Sat, 16 May 2026 17:10:29 +0000</t>
+          <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Worten Marketplace - Portugal y España</t>
+          <t>Update VAT registration information to reinstate Inventory and FBA
+ functionality of your Amazon.it store</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>¡Buenos días!
-Espero que te encuentres bien.
-Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
-Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
-Sobre Worten.
-Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
-En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
-Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
-Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
-Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
-Worten Marketplace tiene una estrategia B2C, c</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 22 May 2026 07:25:40 +0000</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Update VAT registration information to reinstate Inventory and FBA
- functionality of your Amazon.it store</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2296,39 +2248,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2354,39 +2306,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2402,39 +2354,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2459,39 +2411,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2511,39 +2463,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2563,39 +2515,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2615,39 +2567,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2668,39 +2620,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2720,39 +2672,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2772,39 +2724,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2820,39 +2772,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2872,39 +2824,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2924,39 +2876,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2972,39 +2924,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3021,39 +2973,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3073,39 +3025,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -3122,39 +3074,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3171,39 +3123,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3223,39 +3175,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3275,39 +3227,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3324,39 +3276,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3371,39 +3323,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3419,39 +3371,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3471,39 +3423,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3523,39 +3475,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3572,39 +3524,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3624,39 +3576,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3676,39 +3628,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3725,39 +3677,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3777,39 +3729,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3823,91 +3775,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 04/23/26 15:01 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 159.20.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -3932,39 +3832,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -3989,40 +3889,40 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4037,40 +3937,40 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4084,40 +3984,40 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4131,41 +4031,41 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -4176,39 +4076,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4227,39 +4127,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4283,39 +4183,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4333,39 +4233,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4383,39 +4283,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4433,39 +4333,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4483,39 +4383,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4533,39 +4433,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4581,39 +4481,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4631,39 +4531,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4681,39 +4581,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4723,39 +4623,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4776,39 +4676,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4824,39 +4724,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4875,39 +4775,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4918,39 +4818,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4969,39 +4869,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5020,39 +4920,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5071,39 +4971,87 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 16 May 2026 17:10:29 +0000</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C, c</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -5124,39 +5072,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5171,39 +5119,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -5233,39 +5181,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5293,39 +5241,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -5341,39 +5289,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5392,39 +5340,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5446,39 +5394,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5500,39 +5448,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5551,39 +5499,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5595,39 +5543,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5639,39 +5587,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -5683,39 +5631,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5727,39 +5675,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5771,39 +5719,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5815,39 +5763,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5866,39 +5814,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5917,39 +5865,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -5961,39 +5909,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6005,39 +5953,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6049,39 +5997,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6093,39 +6041,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -6137,39 +6085,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6181,39 +6129,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6225,39 +6173,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6269,39 +6217,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6313,39 +6261,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6357,39 +6305,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6401,39 +6349,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6445,39 +6393,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6489,40 +6437,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6541,39 +6489,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6585,39 +6533,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6629,39 +6577,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6673,39 +6621,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6717,39 +6665,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6761,39 +6709,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6814,39 +6762,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6861,39 +6809,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6912,39 +6860,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6966,39 +6914,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -7024,40 +6972,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7073,40 +7021,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7122,39 +7070,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7170,39 +7118,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7218,39 +7166,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7266,39 +7214,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7312,39 +7260,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -7362,40 +7310,40 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7411,39 +7359,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7459,39 +7407,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7507,40 +7455,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7556,39 +7504,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7605,39 +7553,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -7666,39 +7614,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7714,39 +7662,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7760,39 +7708,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7807,39 +7755,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7859,39 +7807,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -7920,40 +7868,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -7966,39 +7914,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -8013,39 +7961,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -8058,40 +8006,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -8106,40 +8054,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -8153,39 +8101,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -8199,39 +8147,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -8246,39 +8194,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -8292,39 +8240,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -8339,39 +8287,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8386,39 +8334,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8437,39 +8385,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -8485,39 +8433,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8538,39 +8486,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -8588,40 +8536,40 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -8639,39 +8587,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -8688,39 +8636,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -8738,40 +8686,40 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -8789,39 +8737,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -8839,88 +8787,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>规划您的 La French Week 促销活动</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>立即规划您的促销
-尊敬的卖家：
-通过为您选定的商品提报Z划算和促销（价格折扣和优惠券），为亚马逊 La French Week 做好准备。
-请为您的产品提报活动期间的促销。
-关键日期
-活动日期： 2026年4月29日至5月5日
-Z划算提报截止日期： 开始日期前1天
-优惠券和价格折扣提报截止日期： 活动结束前 12 小时
-即刻提报您的促销活动 &gt; https://go.amazonsellerservices.com/e/229492/-ld-DC-EM-D419093827-Wk16/7z2ympf/6620349954/h/d9eRPXQyjE3xa9moRJQyNnMughaMjazH89ZvYGbD16o
-您的 ASIN 推荐清单
-以下为您精选推荐的 ASIN，可用于提交至 La French Week。
-&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;站点&lt;/th&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;ASIN&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="padding:10px; border-top:2px solid #868D95; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8944,39 +8843,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8997,39 +8896,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9052,39 +8951,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9108,39 +9007,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9163,39 +9062,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9219,39 +9118,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9275,39 +9174,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9328,39 +9227,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -9369,39 +9268,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9431,39 +9330,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
